--- a/2_kaito/皆藤実験.xlsx
+++ b/2_kaito/皆藤実験.xlsx
@@ -1,20 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/takumi/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C7A862F-0728-1845-86E9-DBE922001A82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD79E51C-1F9B-384F-9C63-DDA3E6A7F472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4420" yWindow="1260" windowWidth="30320" windowHeight="20320" activeTab="1" xr2:uid="{D6BD0E28-90F6-BA44-8F44-AC6BBBE1DE30}"/>
+    <workbookView xWindow="24000" yWindow="1500" windowWidth="30320" windowHeight="20320" activeTab="2" xr2:uid="{D6BD0E28-90F6-BA44-8F44-AC6BBBE1DE30}"/>
   </bookViews>
   <sheets>
     <sheet name="LC" sheetId="1" r:id="rId1"/>
-    <sheet name="RC" sheetId="2" r:id="rId2"/>
+    <sheet name="WB発振 ボード線図" sheetId="2" r:id="rId2"/>
+    <sheet name="WB発振　可変抵抗を変えて発振周波数求める" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="40">
   <si>
     <t>L [μH]</t>
     <phoneticPr fontId="1"/>
@@ -68,16 +70,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>共振周波数(計算) [MHz]</t>
-    <rPh sb="0" eb="5">
-      <t>キョウシｎン</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ケイサｎン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>共振周波数(実測) [kHz]</t>
     <rPh sb="0" eb="5">
       <t>キョウシｎン</t>
@@ -221,6 +213,243 @@
       <t>ゴサル</t>
     </rPh>
     <rPh sb="15" eb="16">
+      <t xml:space="preserve">リツ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>可変抵抗 R4 [Ω]</t>
+    <rPh sb="0" eb="4">
+      <t>カヘｎン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>電圧増幅度A 理論値</t>
+    <rPh sb="0" eb="5">
+      <t>デンアツゾウフ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>リロｎン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>発振を開始した周波数 [kHz]</t>
+    <rPh sb="0" eb="2">
+      <t>ハッシｎン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カイシス</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>シュウｈア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>入力電圧実効値 [V]</t>
+    <rPh sb="0" eb="2">
+      <t>ニュウリョｋウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シュｔウ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ジッコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>発振周波数理論値</t>
+    <rPh sb="0" eb="5">
+      <t>ハッシｎン</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>リロｎン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>20.36k</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>増幅率A</t>
+    <rPh sb="0" eb="3">
+      <t>ゾウフｋウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>帰還率β</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>増幅率*帰還率</t>
+    <rPh sb="0" eb="3">
+      <t>ゾウフｋウ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>キカｎン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>真値を一とする時</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">シンチ </t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>1ｔオ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t xml:space="preserve">トキ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>増幅率誤差率 [%]</t>
+    <rPh sb="0" eb="3">
+      <t>ゾウフｋウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ゴサリｔウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t xml:space="preserve">リツ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>増幅率*帰還率　誤差率 [%]</t>
+    <rPh sb="10" eb="11">
+      <t>リツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">8/7提出
+# 目的
+プリントの内容
+# 原理
+課題に出したやつ
+発振の条件
+フィードバックのブロック図から
+(2)
+トランジスタ増幅回路の電圧増幅率
+エミッタ設置
+直流、交流回路、Hパラメーターを用いた交流回路に変換していく
+電圧増幅率を求める
+ループをしっかり書いて向きを
+2
+ベース接地でも同様に解析
+（3）
+ウィーンブリッジ発振回路
+回路をしっかり書いてから
+1. ターマン型の帰還率(4)しきを導く
+2. 平衡条件から発進条件を求める
+元の回路から増幅率を書かなきゃいけない
+# 実験回路、実験結果、検討
+(1) ハートレーがた発振回路
+結果はまず表で
+理論値と比較
+オープンでも発振したこと、Cを変えていくと
+オープンで発振したことからCがあるはずだということでキャパしタンスを求めて、
+候補を２つ出して
+その容量が元々あると仮定して補正する
+(2) コルピッツ発振回路
+回路ず
+結果
+検討
+オープンにしても発進しなかった
+同じ条件でCが含まれているはず
+(3)ウィーンブリッジ発振秋ろ
+1. ターマン帰還回路のボード線図
+グラフで表現
+グラフの中に位相が0の時のデータを示す
+理論値との比較検討
+2. ウィーンブリッジ発振回路
+回路使いて
+実験結果
+データと平均値を出して発振周波数がいくつかを書く
+比較検討、
+抵抗、増幅率の測定結果と理論値との検討
+8/7提出
+# 目的
+プリントの内容
+# 原理
+課題に出したやつ
+発振の条件
+フィードバックのブロック図から
+(2)
+トランジスタ増幅回路の電圧増幅率
+エミッタ設置
+直流、交流回路、Hパラメーターを用いた交流回路に変換していく
+電圧増幅率を求める
+ループをしっかり書いて向きを
+2
+ベース接地でも同様に解析
+（3）
+ウィーンブリッジ発振回路
+回路をしっかり書いてから
+1. ターマン型の帰還率(4)しきを導く
+2. 平衡条件から発進条件を求める
+元の回路から増幅率を書かなきゃいけない
+# 実験回路、実験結果、検討
+(1) ハートレーがた発振回路
+結果はまず表で
+理論値と比較
+オープンでも発振したこと、Cを変えていくと
+オープンで発振したことからCがあるはずだということでキャパしタンスを求めて、
+候補を２つ出して
+その容量が元々あると仮定して補正する
+(2) コルピッツ発振回路
+回路ず
+結果
+検討
+オープンにしても発進しなかった
+同じ条件でCが含まれているはず
+(3)ウィーンブリッジ発振秋ろ
+1. ターマン帰還回路のボード線図
+グラフで表現
+グラフの中に位相が0の時のデータを示す
+理論値との比較検討
+2. ウィーンブリッジ発振回路
+回路使いて
+実験結果
+データと平均値を出して発振周波数がいくつかを書く
+比較検討、
+抵抗、増幅率の測定結果と理論値との検討
+</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>共振周波数(理論値) [kHz]</t>
+    <rPh sb="0" eb="5">
+      <t>キョウシｎン</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>リロｎン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>共振周波数(理論値) [MHz]</t>
+    <rPh sb="0" eb="5">
+      <t>キョウシｎン</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>リロｎン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>周波数の誤差率</t>
+    <rPh sb="0" eb="3">
+      <t>シュウｈア</t>
+    </rPh>
+    <rPh sb="6" eb="7">
       <t xml:space="preserve">リツ </t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -281,7 +510,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -299,6 +528,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -372,7 +604,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'RC'!$G$2</c:f>
+              <c:f>'WB発振 ボード線図'!$G$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -405,7 +637,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'RC'!$B$3:$B$29</c:f>
+              <c:f>'WB発振 ボード線図'!$B$3:$B$29</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="27"/>
@@ -495,7 +727,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'RC'!$G$3:$G$29</c:f>
+              <c:f>'WB発振 ボード線図'!$G$3:$G$29</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="27"/>
@@ -609,7 +841,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'RC'!$H$2</c:f>
+              <c:f>'WB発振 ボード線図'!$H$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -642,7 +874,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'RC'!$B$3:$B$29</c:f>
+              <c:f>'WB発振 ボード線図'!$B$3:$B$29</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="27"/>
@@ -732,7 +964,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'RC'!$H$3:$H$29</c:f>
+              <c:f>'WB発振 ボード線図'!$H$3:$H$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="27"/>
@@ -1025,6 +1257,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="959704895"/>
+        <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
@@ -2027,7 +2260,7 @@
   <dimension ref="A1:Q18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
-    <col min="4" max="4" width="19.85546875" customWidth="1"/>
+    <col min="4" max="4" width="20.85546875" customWidth="1"/>
     <col min="5" max="5" width="19.28515625" customWidth="1"/>
     <col min="6" max="6" width="10.85546875" customWidth="1"/>
     <col min="7" max="7" width="12.7109375" customWidth="1"/>
@@ -2037,7 +2270,7 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="K1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -2051,19 +2284,19 @@
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J2" s="5"/>
       <c r="K2" t="s">
@@ -2076,16 +2309,16 @@
         <v>2</v>
       </c>
       <c r="N2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -2402,10 +2635,13 @@
     </row>
     <row r="9" spans="1:17">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>10</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9">
@@ -2416,7 +2652,7 @@
       </c>
       <c r="J9" s="5"/>
       <c r="N9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O9" s="3"/>
       <c r="P9">
@@ -2432,7 +2668,7 @@
     </row>
     <row r="11" spans="1:17">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B11" t="s">
         <v>3</v>
@@ -2441,19 +2677,19 @@
         <v>0</v>
       </c>
       <c r="D11" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J11" s="5"/>
     </row>
@@ -2609,10 +2845,13 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="B18" t="s">
+        <v>10</v>
       </c>
       <c r="E18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -2637,25 +2876,25 @@
   <sheetData>
     <row r="2" spans="1:8">
       <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" t="s">
         <v>17</v>
       </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>18</v>
-      </c>
-      <c r="H2" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -3388,7 +3627,7 @@
     </row>
     <row r="31" spans="1:8">
       <c r="B31" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D31" s="1">
         <f>(3344-3300)*100/3344</f>
@@ -3401,4 +3640,175 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{325BBAB3-CBF5-7643-9B5C-77152460A4F8}">
+  <dimension ref="B2:J15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
+  <cols>
+    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" customWidth="1"/>
+    <col min="9" max="9" width="22.5703125" customWidth="1"/>
+    <col min="10" max="10" width="17.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:10">
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10">
+      <c r="B3">
+        <v>3.33</v>
+      </c>
+      <c r="C3">
+        <v>12.9</v>
+      </c>
+      <c r="D3">
+        <v>4.53</v>
+      </c>
+      <c r="E3">
+        <v>12.7</v>
+      </c>
+      <c r="F3">
+        <v>4.41</v>
+      </c>
+      <c r="G3" s="1">
+        <f>($G$8-B3)*100/G8</f>
+        <v>0.29940119760478406</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10">
+      <c r="B4">
+        <v>3.33</v>
+      </c>
+      <c r="C4" s="1">
+        <v>13</v>
+      </c>
+      <c r="D4">
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="E4">
+        <v>12.7</v>
+      </c>
+      <c r="F4">
+        <v>4.49</v>
+      </c>
+      <c r="G4" s="1">
+        <f>($G$8-B4)*100/$G$8</f>
+        <v>0.29940119760478406</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10">
+      <c r="G7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10">
+      <c r="G8">
+        <v>3.34</v>
+      </c>
+      <c r="H8">
+        <v>3.02</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10">
+      <c r="F12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" t="s">
+        <v>30</v>
+      </c>
+      <c r="I12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10">
+      <c r="F13" t="s">
+        <v>29</v>
+      </c>
+      <c r="G13" s="3">
+        <f>1+20360/9990</f>
+        <v>3.0380380380380378</v>
+      </c>
+      <c r="I13" s="1">
+        <f>(H8-G13)*100/H8</f>
+        <v>-0.59728602774959694</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10">
+      <c r="F14" t="s">
+        <v>31</v>
+      </c>
+      <c r="H14" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" t="s">
+        <v>35</v>
+      </c>
+      <c r="J14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10">
+      <c r="F15">
+        <v>0.32300000000000001</v>
+      </c>
+      <c r="H15" s="4">
+        <f>G13*F15</f>
+        <v>0.98128628628628622</v>
+      </c>
+      <c r="I15" s="1">
+        <f>(1-H15)*100/H15</f>
+        <v>1.9070595375928985</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AD57A07-B246-E44C-AC45-62ED713300BB}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
+  <cols>
+    <col min="1" max="1" width="69.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="408" customHeight="1">
+      <c r="A1" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>